--- a/backend/examples/excel/最小示例.xlsx
+++ b/backend/examples/excel/最小示例.xlsx
@@ -72,27 +72,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">公司 / 账号 / 预置合同属于运行期内容，不在表格里：</t>
+          <t xml:space="preserve">合同类型只写脚本路径（examples/contracts/mini_contracts.py），四份 JSON 由代码产出。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  · 建完框架后到「公司管理」建公司、到「账号管理」建账号、到「合同管理」建合同；</t>
+          <t xml:space="preserve">公司 / 账号 / 预置合同属于运行期内容，不在表格里：</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  · 建完框架后到「公司管理」建公司、到「账号管理」建账号、到「合同管理」建合同；</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  · 想一次建齐可参考 examples/competitions/auto_chain_competition.py（代码建包）。</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">用法：python examples/excel/build_from_sheets.py examples/excel/最小示例.xlsx --create-competition</t>
         </is>
@@ -455,45 +462,15 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t xml:space="preserve">脚本路径</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t xml:space="preserve">类型标识</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合同名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">脚本路径</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">参与方</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输入项定义</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">效果定义</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前置检查</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t xml:space="preserve">是否启用</t>
         </is>
@@ -502,40 +479,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">examples/contracts/mini_contracts.py</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t xml:space="preserve">mini-sale</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">简易购销合同</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">买方付钱给卖方</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">seller=卖方; buyer=买方</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[{"key": "amount", "label": "成交金额", "type": "NUMBER", "required": true, "default": "1000"}]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[{"kind": "FIELD", "party": "buyer", "fieldKey": "cash", "op": "SUB", "value": {"type": "INPUT", "key": "amount"}}, {"kind": "FIELD", "party": "seller", "fieldKey": "cash", "op": "ADD", "value": {"type": "INPUT", "key": "amount"}}]</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[{"kind": "FIELD_COMPARE", "party": "buyer", "fieldKey": "cash", "op": "GTE", "value": {"type": "INPUT", "key": "amount"}, "errorMessage": "买方现金不足以支付货款"}]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">是</t>
         </is>
